--- a/Input/instrumento n6_cp2_limpio.xlsx
+++ b/Input/instrumento n6_cp2_limpio.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0340f46c4e5df8d5/Escritorio/OPT_R1/Input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0340f46c4e5df8d5/Escritorio/Cuidados/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="987" documentId="13_ncr:1_{E42A7D12-2DF1-41EF-9304-A16BC4052AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{801559CF-CDE4-4706-8FB0-DC608FF34501}"/>
+  <xr:revisionPtr revIDLastSave="989" documentId="13_ncr:1_{E42A7D12-2DF1-41EF-9304-A16BC4052AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B74F791-0128-401E-9D10-00E6E4074360}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F491E6BB-27A6-4656-8C8B-02D8962D134E}"/>
   </bookViews>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="772">
   <si>
-    <t>Persona dependiente</t>
-  </si>
-  <si>
     <t>RUN</t>
   </si>
   <si>
@@ -83,9 +80,6 @@
     <t>Región</t>
   </si>
   <si>
-    <t>Teléfono 1</t>
-  </si>
-  <si>
     <t>Teléfono 2</t>
   </si>
   <si>
@@ -2352,6 +2346,12 @@
   </si>
   <si>
     <t>casa roja, al costado de taller mecánco</t>
+  </si>
+  <si>
+    <t>Persona_dependiente</t>
+  </si>
+  <si>
+    <t>Teléfono_1</t>
   </si>
 </sst>
 </file>
@@ -2492,10 +2492,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2823,126 +2819,126 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
+      <c r="U1" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="F2" s="4">
         <v>2</v>
@@ -2957,7 +2953,7 @@
         <v>63</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K2" s="7">
         <v>2794</v>
@@ -2972,10 +2968,10 @@
         <v>98</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q2" s="3">
         <v>930911822</v>
@@ -3037,19 +3033,19 @@
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F3" s="4">
         <v>2</v>
@@ -3064,7 +3060,7 @@
         <v>49</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K3" s="7">
         <v>2281</v>
@@ -3079,10 +3075,10 @@
         <v>98</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q3" s="3">
         <v>976020667</v>
@@ -3144,19 +3140,19 @@
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F4" s="4">
         <v>2</v>
@@ -3171,7 +3167,7 @@
         <v>47</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K4" s="7">
         <v>1885</v>
@@ -3186,10 +3182,10 @@
         <v>98</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q4" s="3">
         <v>965408375</v>
@@ -3251,19 +3247,19 @@
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="F5" s="4">
         <v>2</v>
@@ -3278,7 +3274,7 @@
         <v>63</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K5" s="7">
         <v>2698</v>
@@ -3293,10 +3289,10 @@
         <v>98</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q5" s="3">
         <v>961148189</v>
@@ -3358,19 +3354,19 @@
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="F6" s="4">
         <v>2</v>
@@ -3385,7 +3381,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K6" s="7">
         <v>2294</v>
@@ -3400,10 +3396,10 @@
         <v>98</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q6" s="3">
         <v>972210910</v>
@@ -3465,19 +3461,19 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="F7" s="4">
         <v>2</v>
@@ -3492,7 +3488,7 @@
         <v>56</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K7" s="7">
         <v>9721</v>
@@ -3507,10 +3503,10 @@
         <v>98</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q7" s="3">
         <v>978732582</v>
@@ -3572,19 +3568,19 @@
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="F8" s="4">
         <v>2</v>
@@ -3599,7 +3595,7 @@
         <v>51</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K8" s="7">
         <v>1660</v>
@@ -3614,10 +3610,10 @@
         <v>98</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q8" s="3">
         <v>975007049</v>
@@ -3679,19 +3675,19 @@
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="F9" s="4">
         <v>2</v>
@@ -3706,7 +3702,7 @@
         <v>43</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K9" s="7">
         <v>851</v>
@@ -3721,10 +3717,10 @@
         <v>98</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q9" s="3">
         <v>932797463</v>
@@ -3786,19 +3782,19 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F10" s="4">
         <v>2</v>
@@ -3813,13 +3809,13 @@
         <v>84</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K10" s="7">
         <v>1102</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M10" s="3">
         <v>98</v>
@@ -3828,10 +3824,10 @@
         <v>98</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q10" s="3">
         <v>939156525</v>
@@ -3893,19 +3889,19 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="F11" s="4">
         <v>2</v>
@@ -3920,7 +3916,7 @@
         <v>51</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K11" s="7">
         <v>1048</v>
@@ -3932,13 +3928,13 @@
         <v>98</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q11" s="3">
         <v>986007911</v>
@@ -4000,19 +3996,19 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
+        <v>646</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>650</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>652</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -4027,7 +4023,7 @@
         <v>22</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="K12" s="7">
         <v>1666</v>
@@ -4042,10 +4038,10 @@
         <v>98</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q12" s="3">
         <v>976069328</v>
@@ -4107,25 +4103,25 @@
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="F13" s="4">
+        <v>2</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F13" s="4">
-        <v>2</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>94</v>
       </c>
       <c r="H13" s="8">
         <v>28189</v>
@@ -4134,7 +4130,7 @@
         <v>49</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K13" s="7">
         <v>2780</v>
@@ -4149,10 +4145,10 @@
         <v>98</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q13" s="3">
         <v>987385062</v>
@@ -4214,19 +4210,19 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="E14" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F14" s="4">
         <v>2</v>
@@ -4241,7 +4237,7 @@
         <v>59</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K14" s="3">
         <v>1835</v>
@@ -4256,10 +4252,10 @@
         <v>98</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q14" s="3">
         <v>934140565</v>
@@ -4321,19 +4317,19 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="F15" s="4">
         <v>2</v>
@@ -4348,7 +4344,7 @@
         <v>71</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K15" s="3">
         <v>1515</v>
@@ -4363,10 +4359,10 @@
         <v>98</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q15" s="3">
         <v>977500432</v>
@@ -4428,25 +4424,25 @@
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
+        <v>652</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F16" s="4">
+        <v>2</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>656</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="F16" s="4">
-        <v>2</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>658</v>
       </c>
       <c r="H16" s="8">
         <v>34954</v>
@@ -4455,7 +4451,7 @@
         <v>30</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K16" s="3">
         <v>1709</v>
@@ -4470,10 +4466,10 @@
         <v>98</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q16" s="3">
         <v>930618424</v>
@@ -4535,25 +4531,25 @@
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="F17" s="4">
+        <v>2</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F17" s="4">
-        <v>2</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>113</v>
       </c>
       <c r="H17" s="8">
         <v>22113</v>
@@ -4562,7 +4558,7 @@
         <v>66</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K17" s="3">
         <v>1069</v>
@@ -4577,10 +4573,10 @@
         <v>98</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q17" s="3">
         <v>997849470</v>
@@ -4642,19 +4638,19 @@
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="F18" s="4">
         <v>2</v>
@@ -4669,7 +4665,7 @@
         <v>57</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="K18" s="3">
         <v>2515</v>
@@ -4684,10 +4680,10 @@
         <v>98</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q18" s="3">
         <v>987276319</v>
@@ -4749,19 +4745,19 @@
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="F19" s="4">
         <v>2</v>
@@ -4776,7 +4772,7 @@
         <v>85</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K19" s="3">
         <v>1184</v>
@@ -4791,10 +4787,10 @@
         <v>98</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q19" s="3">
         <v>997795606</v>
@@ -4856,25 +4852,25 @@
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="F20" s="4">
+        <v>2</v>
+      </c>
+      <c r="G20" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F20" s="4">
-        <v>2</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>131</v>
       </c>
       <c r="H20" s="8">
         <v>23400</v>
@@ -4883,7 +4879,7 @@
         <v>62</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K20" s="3">
         <v>2831</v>
@@ -4898,10 +4894,10 @@
         <v>98</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q20" s="3">
         <v>977079690</v>
@@ -4963,25 +4959,25 @@
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
+        <v>763</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>764</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>765</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="D21" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>766</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="F21" s="4">
+        <v>2</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>767</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>768</v>
-      </c>
-      <c r="F21" s="4">
-        <v>2</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>769</v>
       </c>
       <c r="H21" s="8">
         <v>16737</v>
@@ -4990,7 +4986,7 @@
         <v>80</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="K21" s="3">
         <v>1235</v>
@@ -4999,16 +4995,16 @@
         <v>98</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q21" s="3">
         <v>937366512</v>
@@ -5017,7 +5013,7 @@
         <v>96235775</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="T21" s="7">
         <v>10</v>
@@ -5070,19 +5066,19 @@
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="F22" s="4">
         <v>2</v>
@@ -5097,7 +5093,7 @@
         <v>64</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K22" s="3">
         <v>1602</v>
@@ -5112,10 +5108,10 @@
         <v>98</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q22" s="3">
         <v>988323071</v>
@@ -5177,25 +5173,25 @@
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="F23" s="4">
+        <v>2</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="F23" s="4">
-        <v>2</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>144</v>
       </c>
       <c r="H23" s="8">
         <v>18758</v>
@@ -5204,7 +5200,7 @@
         <v>76</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="K23" s="3">
         <v>2392</v>
@@ -5219,10 +5215,10 @@
         <v>98</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q23" s="3">
         <v>994864737</v>
@@ -5284,19 +5280,19 @@
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="F24" s="4">
         <v>2</v>
@@ -5311,7 +5307,7 @@
         <v>36</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K24" s="3">
         <v>843</v>
@@ -5326,10 +5322,10 @@
         <v>98</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q24" s="3">
         <v>945355446</v>
@@ -5338,7 +5334,7 @@
         <v>99</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="T24" s="3">
         <v>16</v>
@@ -5391,25 +5387,25 @@
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="F25" s="4">
+        <v>1</v>
+      </c>
+      <c r="G25" s="10" t="s">
         <v>156</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F25" s="4">
-        <v>1</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="H25" s="8">
         <v>21609</v>
@@ -5418,7 +5414,7 @@
         <v>67</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K25" s="3">
         <v>2906</v>
@@ -5430,13 +5426,13 @@
         <v>98</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q25" s="3">
         <v>987526801</v>
@@ -5498,19 +5494,19 @@
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="F26" s="4">
         <v>2</v>
@@ -5525,7 +5521,7 @@
         <v>44</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K26" s="3">
         <v>1351</v>
@@ -5540,10 +5536,10 @@
         <v>98</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q26" s="3">
         <v>948070737</v>
@@ -5605,19 +5601,19 @@
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="F27" s="4">
         <v>1</v>
@@ -5632,7 +5628,7 @@
         <v>67</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K27" s="3">
         <v>2139</v>
@@ -5647,10 +5643,10 @@
         <v>98</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q27" s="3">
         <v>942462103</v>
@@ -5712,19 +5708,19 @@
     </row>
     <row r="28" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="F28" s="4">
         <v>2</v>
@@ -5739,7 +5735,7 @@
         <v>38</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K28" s="3">
         <v>1550</v>
@@ -5754,10 +5750,10 @@
         <v>98</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q28" s="3">
         <v>965597675</v>
@@ -5819,19 +5815,19 @@
     </row>
     <row r="29" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A29" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="F29" s="4">
         <v>2</v>
@@ -5846,7 +5842,7 @@
         <v>86</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K29" s="3">
         <v>1983</v>
@@ -5861,10 +5857,10 @@
         <v>98</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q29" s="3">
         <v>986548193</v>
@@ -5926,19 +5922,19 @@
     </row>
     <row r="30" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A30" s="20" t="s">
+        <v>707</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>708</v>
+      </c>
+      <c r="C30" s="12" t="s">
         <v>709</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="D30" s="12" t="s">
         <v>710</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>711</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>712</v>
-      </c>
       <c r="E30" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F30" s="4">
         <v>2</v>
@@ -5953,7 +5949,7 @@
         <v>63</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="K30" s="3">
         <v>1198</v>
@@ -5968,10 +5964,10 @@
         <v>98</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P30" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q30" s="3">
         <v>966145155</v>
@@ -6033,19 +6029,19 @@
     </row>
     <row r="31" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>190</v>
       </c>
       <c r="F31" s="4">
         <v>2</v>
@@ -6060,7 +6056,7 @@
         <v>39</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K31" s="3">
         <v>1081</v>
@@ -6075,10 +6071,10 @@
         <v>98</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q31" s="3">
         <v>965191966</v>
@@ -6140,19 +6136,19 @@
     </row>
     <row r="32" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="F32" s="4">
         <v>2</v>
@@ -6167,13 +6163,13 @@
         <v>62</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K32" s="3">
         <v>837</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M32" s="3">
         <v>98</v>
@@ -6182,10 +6178,10 @@
         <v>98</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q32" s="3">
         <v>981217405</v>
@@ -6247,19 +6243,19 @@
     </row>
     <row r="33" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>203</v>
       </c>
       <c r="F33" s="4">
         <v>1</v>
@@ -6274,7 +6270,7 @@
         <v>67</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K33" s="3">
         <v>921</v>
@@ -6283,16 +6279,16 @@
         <v>98</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q33" s="3">
         <v>990373637</v>
@@ -6354,19 +6350,19 @@
     </row>
     <row r="34" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A34" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>660</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>662</v>
       </c>
       <c r="F34" s="4">
         <v>2</v>
@@ -6381,7 +6377,7 @@
         <v>57</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K34" s="3">
         <v>2297</v>
@@ -6390,16 +6386,16 @@
         <v>98</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q34" s="3">
         <v>957714568</v>
@@ -6461,25 +6457,25 @@
     </row>
     <row r="35" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A35" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="F35" s="4">
+        <v>2</v>
+      </c>
+      <c r="G35" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F35" s="4">
-        <v>2</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="H35" s="8">
         <v>17620</v>
@@ -6488,7 +6484,7 @@
         <v>78</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K35" s="3">
         <v>1864</v>
@@ -6503,10 +6499,10 @@
         <v>98</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q35" s="3">
         <v>999023549</v>
@@ -6568,19 +6564,19 @@
     </row>
     <row r="36" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="F36" s="4">
         <v>2</v>
@@ -6595,7 +6591,7 @@
         <v>67</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K36" s="3">
         <v>920</v>
@@ -6607,13 +6603,13 @@
         <v>98</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q36" s="3">
         <v>962385158</v>
@@ -6675,19 +6671,19 @@
     </row>
     <row r="37" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A37" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="F37" s="4">
         <v>2</v>
@@ -6702,7 +6698,7 @@
         <v>68</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K37" s="3">
         <v>1670</v>
@@ -6711,16 +6707,16 @@
         <v>6</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N37" s="3">
         <v>98</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q37" s="3">
         <v>939340290</v>
@@ -6782,19 +6778,19 @@
     </row>
     <row r="38" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A38" s="18" t="s">
+        <v>663</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="C38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>666</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>668</v>
       </c>
       <c r="F38" s="4">
         <v>2</v>
@@ -6809,7 +6805,7 @@
         <v>59</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="K38" s="3">
         <v>987</v>
@@ -6818,16 +6814,16 @@
         <v>1</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N38" s="3">
         <v>98</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q38" s="3">
         <v>934391049</v>
@@ -6889,19 +6885,19 @@
     </row>
     <row r="39" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A39" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="D39" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="F39" s="4">
         <v>2</v>
@@ -6916,7 +6912,7 @@
         <v>29</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K39" s="3">
         <v>1288</v>
@@ -6931,10 +6927,10 @@
         <v>98</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q39" s="3">
         <v>987647801</v>
@@ -6996,19 +6992,19 @@
     </row>
     <row r="40" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A40" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="F40" s="4">
         <v>2</v>
@@ -7023,7 +7019,7 @@
         <v>54</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K40" s="3">
         <v>2437</v>
@@ -7038,10 +7034,10 @@
         <v>98</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q40" s="3">
         <v>942921617</v>
@@ -7103,19 +7099,19 @@
     </row>
     <row r="41" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A41" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="E41" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="F41" s="4">
         <v>2</v>
@@ -7130,7 +7126,7 @@
         <v>41</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K41" s="3">
         <v>1751</v>
@@ -7145,10 +7141,10 @@
         <v>98</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q41" s="3">
         <v>922095390</v>
@@ -7210,19 +7206,19 @@
     </row>
     <row r="42" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A42" s="20" t="s">
+        <v>712</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>713</v>
+      </c>
+      <c r="C42" s="12" t="s">
         <v>714</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="D42" s="12" t="s">
         <v>715</v>
       </c>
-      <c r="C42" s="12" t="s">
-        <v>716</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>717</v>
-      </c>
       <c r="E42" s="12" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="F42" s="4">
         <v>1</v>
@@ -7237,7 +7233,7 @@
         <v>78</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="K42" s="3">
         <v>1468</v>
@@ -7249,13 +7245,13 @@
         <v>98</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="O42" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P42" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q42" s="3">
         <v>995502528</v>
@@ -7317,25 +7313,25 @@
     </row>
     <row r="43" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A43" s="20" t="s">
+        <v>718</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>719</v>
+      </c>
+      <c r="C43" s="12" t="s">
         <v>720</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="D43" s="12" t="s">
         <v>721</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="E43" s="12" t="s">
         <v>722</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="F43" s="4">
+        <v>2</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>723</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>724</v>
-      </c>
-      <c r="F43" s="4">
-        <v>2</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>725</v>
       </c>
       <c r="H43" s="8">
         <v>24437</v>
@@ -7344,13 +7340,13 @@
         <v>59</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="K43" s="3">
         <v>2716</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="M43" s="3">
         <v>98</v>
@@ -7359,10 +7355,10 @@
         <v>98</v>
       </c>
       <c r="O43" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P43" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q43" s="3">
         <v>958103199</v>
@@ -7424,19 +7420,19 @@
     </row>
     <row r="44" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A44" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="E44" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>249</v>
       </c>
       <c r="F44" s="4">
         <v>2</v>
@@ -7451,7 +7447,7 @@
         <v>54</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K44" s="3">
         <v>736</v>
@@ -7466,10 +7462,10 @@
         <v>98</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q44" s="3">
         <v>956963448</v>
@@ -7531,19 +7527,19 @@
     </row>
     <row r="45" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A45" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="F45" s="4">
         <v>1</v>
@@ -7558,7 +7554,7 @@
         <v>77</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K45" s="3">
         <v>869</v>
@@ -7573,10 +7569,10 @@
         <v>98</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q45" s="3">
         <v>981262189</v>
@@ -7638,19 +7634,19 @@
     </row>
     <row r="46" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A46" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="F46" s="4">
         <v>2</v>
@@ -7665,7 +7661,7 @@
         <v>78</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K46" s="3">
         <v>1424</v>
@@ -7680,10 +7676,10 @@
         <v>98</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q46" s="3">
         <v>994747338</v>
@@ -7745,19 +7741,19 @@
     </row>
     <row r="47" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A47" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="E47" s="3" t="s">
         <v>264</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="F47" s="4">
         <v>2</v>
@@ -7772,25 +7768,25 @@
         <v>77</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K47" s="3">
         <v>1122</v>
       </c>
       <c r="L47" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="N47" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="O47" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q47" s="3">
         <v>921733209</v>
@@ -7852,19 +7848,19 @@
     </row>
     <row r="48" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A48" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="E48" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F48" s="4">
         <v>2</v>
@@ -7879,7 +7875,7 @@
         <v>77</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K48" s="3">
         <v>2186</v>
@@ -7894,10 +7890,10 @@
         <v>98</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q48" s="3">
         <v>223026484</v>
@@ -7959,19 +7955,19 @@
     </row>
     <row r="49" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A49" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>279</v>
-      </c>
       <c r="E49" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F49" s="4">
         <v>2</v>
@@ -7986,25 +7982,25 @@
         <v>69</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="K49" s="3">
         <v>2016</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N49" s="3">
         <v>98</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q49" s="3">
         <v>923786301</v>
@@ -8066,19 +8062,19 @@
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A50" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="F50" s="4">
         <v>2</v>
@@ -8093,13 +8089,13 @@
         <v>51</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="K50" s="3">
         <v>2701</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M50" s="3">
         <v>98</v>
@@ -8108,10 +8104,10 @@
         <v>98</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q50" s="3">
         <v>951940028</v>
@@ -8173,19 +8169,19 @@
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A51" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="E51" s="3" t="s">
         <v>289</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>291</v>
       </c>
       <c r="F51" s="4">
         <v>2</v>
@@ -8200,13 +8196,13 @@
         <v>64</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="K51" s="3">
         <v>1841</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M51" s="3">
         <v>98</v>
@@ -8215,10 +8211,10 @@
         <v>98</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q51" s="3">
         <v>945332555</v>
@@ -8280,19 +8276,19 @@
     </row>
     <row r="52" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A52" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="F52" s="4">
         <v>2</v>
@@ -8307,7 +8303,7 @@
         <v>59</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K52" s="3">
         <v>1835</v>
@@ -8322,10 +8318,10 @@
         <v>98</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q52" s="3">
         <v>934140565</v>
@@ -8387,19 +8383,19 @@
     </row>
     <row r="53" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A53" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="E53" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>300</v>
       </c>
       <c r="F53" s="4">
         <v>1</v>
@@ -8414,7 +8410,7 @@
         <v>46</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="K53" s="3">
         <v>1365</v>
@@ -8429,10 +8425,10 @@
         <v>98</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q53" s="3">
         <v>979382377</v>
@@ -8494,19 +8490,19 @@
     </row>
     <row r="54" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A54" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="E54" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>306</v>
       </c>
       <c r="F54" s="4">
         <v>2</v>
@@ -8521,7 +8517,7 @@
         <v>52</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="K54" s="3">
         <v>1220</v>
@@ -8536,10 +8532,10 @@
         <v>98</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q54" s="3">
         <v>963392811</v>
@@ -8601,19 +8597,19 @@
     </row>
     <row r="55" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A55" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="D55" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>312</v>
       </c>
       <c r="F55" s="4">
         <v>2</v>
@@ -8628,7 +8624,7 @@
         <v>40</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="K55" s="3">
         <v>2375</v>
@@ -8643,10 +8639,10 @@
         <v>98</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q55" s="3">
         <v>976470820</v>
@@ -8708,19 +8704,19 @@
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A56" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="E56" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>318</v>
       </c>
       <c r="F56" s="4">
         <v>2</v>
@@ -8735,7 +8731,7 @@
         <v>68</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K56" s="3">
         <v>1156</v>
@@ -8750,10 +8746,10 @@
         <v>98</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q56" s="3">
         <v>988824034</v>
@@ -8815,19 +8811,19 @@
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A57" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="E57" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>324</v>
       </c>
       <c r="F57" s="4">
         <v>2</v>
@@ -8842,7 +8838,7 @@
         <v>48</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="K57" s="3">
         <v>435</v>
@@ -8857,10 +8853,10 @@
         <v>98</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q57" s="3">
         <v>930148311</v>
@@ -8922,19 +8918,19 @@
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A58" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="E58" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>330</v>
       </c>
       <c r="F58" s="4">
         <v>2</v>
@@ -8949,7 +8945,7 @@
         <v>66</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="K58" s="3">
         <v>2511</v>
@@ -8958,16 +8954,16 @@
         <v>98</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N58" s="3">
         <v>98</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q58" s="3">
         <v>981240670</v>
@@ -9029,19 +9025,19 @@
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A59" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="D59" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="E59" s="3" t="s">
         <v>335</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>337</v>
       </c>
       <c r="F59" s="4">
         <v>2</v>
@@ -9056,7 +9052,7 @@
         <v>50</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="K59" s="3">
         <v>1272</v>
@@ -9065,16 +9061,16 @@
         <v>98</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="N59" s="3">
         <v>98</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q59" s="3">
         <v>990171937</v>
@@ -9136,19 +9132,19 @@
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A60" s="18" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C60" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>550</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>552</v>
       </c>
       <c r="F60" s="4">
         <v>2</v>
@@ -9163,7 +9159,7 @@
         <v>55</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="K60" s="3">
         <v>1605</v>
@@ -9178,10 +9174,10 @@
         <v>98</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q60" s="3">
         <v>979960221</v>
@@ -9243,19 +9239,19 @@
     </row>
     <row r="61" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A61" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="D61" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="E61" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="F61" s="4">
         <v>2</v>
@@ -9270,10 +9266,10 @@
         <v>77</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="L61" s="3">
         <v>98</v>
@@ -9283,10 +9279,10 @@
         <v>98</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q61" s="3">
         <v>956792068</v>
@@ -9348,19 +9344,19 @@
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A62" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>349</v>
-      </c>
       <c r="E62" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F62" s="4">
         <v>2</v>
@@ -9375,7 +9371,7 @@
         <v>75</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K62" s="3">
         <v>2051</v>
@@ -9390,10 +9386,10 @@
         <v>98</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q62" s="3">
         <v>989863324</v>
@@ -9455,19 +9451,19 @@
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A63" s="20" t="s">
+        <v>726</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="C63" s="12" t="s">
         <v>728</v>
       </c>
-      <c r="B63" s="12" t="s">
-        <v>729</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>730</v>
-      </c>
       <c r="D63" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F63" s="4">
         <v>2</v>
@@ -9482,13 +9478,13 @@
         <v>84</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="K63" s="3">
         <v>1499</v>
       </c>
       <c r="L63" s="10" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="M63" s="3">
         <v>98</v>
@@ -9497,10 +9493,10 @@
         <v>98</v>
       </c>
       <c r="O63" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P63" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q63" s="3">
         <v>97166893</v>
@@ -9562,19 +9558,19 @@
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A64" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="D64" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="E64" s="3" t="s">
         <v>353</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>355</v>
       </c>
       <c r="F64" s="4">
         <v>1</v>
@@ -9589,7 +9585,7 @@
         <v>52</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="K64" s="3">
         <v>2851</v>
@@ -9604,10 +9600,10 @@
         <v>98</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q64" s="3">
         <v>961727651</v>
@@ -9669,19 +9665,19 @@
     </row>
     <row r="65" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A65" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="D65" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="E65" s="3" t="s">
         <v>359</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>361</v>
       </c>
       <c r="F65" s="4">
         <v>1</v>
@@ -9696,7 +9692,7 @@
         <v>68</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="K65" s="3">
         <v>1051</v>
@@ -9711,10 +9707,10 @@
         <v>98</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q65" s="3">
         <v>992400217</v>
@@ -9776,19 +9772,19 @@
     </row>
     <row r="66" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A66" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="D66" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>366</v>
-      </c>
       <c r="E66" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F66" s="4">
         <v>2</v>
@@ -9803,13 +9799,13 @@
         <v>56</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="K66" s="3">
         <v>1390</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="M66" s="3">
         <v>98</v>
@@ -9818,10 +9814,10 @@
         <v>98</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q66" s="3">
         <v>974958023</v>
@@ -9883,19 +9879,19 @@
     </row>
     <row r="67" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A67" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="D67" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="E67" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>373</v>
       </c>
       <c r="F67" s="4">
         <v>2</v>
@@ -9910,7 +9906,7 @@
         <v>45</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="K67" s="3">
         <v>2774</v>
@@ -9919,16 +9915,16 @@
         <v>98</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="N67" s="3">
         <v>98</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q67" s="3">
         <v>950122513</v>
@@ -9990,19 +9986,19 @@
     </row>
     <row r="68" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A68" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>379</v>
-      </c>
       <c r="E68" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F68" s="4">
         <v>2</v>
@@ -10017,7 +10013,7 @@
         <v>46</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="K68" s="3">
         <v>733</v>
@@ -10032,10 +10028,10 @@
         <v>98</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q68" s="3">
         <v>958804560</v>
@@ -10097,19 +10093,19 @@
     </row>
     <row r="69" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A69" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="E69" s="3" t="s">
         <v>382</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>384</v>
       </c>
       <c r="F69" s="4">
         <v>2</v>
@@ -10124,7 +10120,7 @@
         <v>62</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="K69" s="3">
         <v>2696</v>
@@ -10139,10 +10135,10 @@
         <v>98</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q69" s="3">
         <v>974451632</v>
@@ -10204,19 +10200,19 @@
     </row>
     <row r="70" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>388</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>390</v>
       </c>
       <c r="F70" s="4">
         <v>2</v>
@@ -10231,7 +10227,7 @@
         <v>62</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="K70" s="3">
         <v>2746</v>
@@ -10246,10 +10242,10 @@
         <v>98</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q70" s="3">
         <v>952217336</v>
@@ -10311,19 +10307,19 @@
     </row>
     <row r="71" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A71" s="18" t="s">
+        <v>671</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>676</v>
-      </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F71" s="4">
         <v>2</v>
@@ -10338,13 +10334,13 @@
         <v>72</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="K71" s="3">
         <v>1699</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="M71" s="3">
         <v>98</v>
@@ -10353,10 +10349,10 @@
         <v>98</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q71" s="3">
         <v>976059592</v>
@@ -10418,19 +10414,19 @@
     </row>
     <row r="72" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A72" s="20" t="s">
+        <v>677</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>678</v>
+      </c>
+      <c r="C72" s="12" t="s">
         <v>679</v>
       </c>
-      <c r="B72" s="12" t="s">
+      <c r="D72" s="12" t="s">
         <v>680</v>
       </c>
-      <c r="C72" s="12" t="s">
-        <v>681</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>682</v>
-      </c>
       <c r="E72" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F72" s="4">
         <v>2</v>
@@ -10445,25 +10441,25 @@
         <v>62</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K72" s="3">
         <v>1021</v>
       </c>
       <c r="L72" s="10" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="M72" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N72" s="3">
         <v>98</v>
       </c>
       <c r="O72" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P72" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q72" s="3">
         <v>986098669</v>
@@ -10525,19 +10521,19 @@
     </row>
     <row r="73" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A73" s="20" t="s">
+        <v>682</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="C73" s="12" t="s">
         <v>684</v>
       </c>
-      <c r="B73" s="12" t="s">
+      <c r="D73" s="12" t="s">
         <v>685</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="E73" s="12" t="s">
         <v>686</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>687</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>688</v>
       </c>
       <c r="F73" s="4">
         <v>2</v>
@@ -10552,7 +10548,7 @@
         <v>63</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="K73" s="3">
         <v>743</v>
@@ -10567,10 +10563,10 @@
         <v>98</v>
       </c>
       <c r="O73" s="12" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="P73" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q73" s="3">
         <v>977139764</v>
@@ -10632,19 +10628,19 @@
     </row>
     <row r="74" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A74" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="D74" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>395</v>
       </c>
       <c r="F74" s="4">
         <v>1</v>
@@ -10659,25 +10655,25 @@
         <v>54</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="K74" s="7">
         <v>986</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q74" s="3">
         <v>998813952</v>
@@ -10739,19 +10735,19 @@
     </row>
     <row r="75" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A75" s="18" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="E75" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F75" s="4">
         <v>2</v>
@@ -10766,7 +10762,7 @@
         <v>41</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K75" s="7">
         <v>1751</v>
@@ -10781,10 +10777,10 @@
         <v>98</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q75" s="3">
         <v>922095390</v>
@@ -10846,25 +10842,25 @@
     </row>
     <row r="76" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A76" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="D76" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="E76" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="F76" s="4">
+        <v>2</v>
+      </c>
+      <c r="G76" s="10" t="s">
         <v>404</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="F76" s="4">
-        <v>2</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>406</v>
       </c>
       <c r="H76" s="8">
         <v>24807</v>
@@ -10873,7 +10869,7 @@
         <v>58</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="K76" s="7">
         <v>2701</v>
@@ -10885,13 +10881,13 @@
         <v>98</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q76" s="3">
         <v>99</v>
@@ -10953,19 +10949,19 @@
     </row>
     <row r="77" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A77" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="D77" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="F77" s="4">
         <v>2</v>
@@ -10980,7 +10976,7 @@
         <v>61</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="K77" s="7">
         <v>1487</v>
@@ -10989,16 +10985,16 @@
         <v>98</v>
       </c>
       <c r="M77" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="N77" s="3">
         <v>98</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q77" s="3">
         <v>956161036</v>
@@ -11060,19 +11056,19 @@
     </row>
     <row r="78" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A78" s="18" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C78" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="F78" s="4">
         <v>2</v>
@@ -11087,7 +11083,7 @@
         <v>65</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K78" s="7">
         <v>1602</v>
@@ -11102,10 +11098,10 @@
         <v>98</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q78" s="3">
         <v>988323071</v>
@@ -11167,19 +11163,19 @@
     </row>
     <row r="79" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A79" s="18" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="E79" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F79" s="4">
         <v>2</v>
@@ -11194,7 +11190,7 @@
         <v>41</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K79" s="7">
         <v>1751</v>
@@ -11209,10 +11205,10 @@
         <v>98</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q79" s="3">
         <v>922095390</v>
@@ -11274,19 +11270,19 @@
     </row>
     <row r="80" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A80" s="18" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C80" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>249</v>
       </c>
       <c r="F80" s="4">
         <v>2</v>
@@ -11301,7 +11297,7 @@
         <v>54</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K80" s="7">
         <v>367</v>
@@ -11316,10 +11312,10 @@
         <v>98</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q80" s="3">
         <v>956963448</v>
@@ -11381,19 +11377,19 @@
     </row>
     <row r="81" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A81" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="D81" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="E81" s="3" t="s">
         <v>421</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>423</v>
       </c>
       <c r="F81" s="4">
         <v>1</v>
@@ -11408,7 +11404,7 @@
         <v>62</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K81" s="7">
         <v>1880</v>
@@ -11423,10 +11419,10 @@
         <v>98</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q81" s="3">
         <v>999473643</v>
@@ -11488,19 +11484,19 @@
     </row>
     <row r="82" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A82" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="D82" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="E82" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>428</v>
       </c>
       <c r="F82" s="4">
         <v>1</v>
@@ -11515,13 +11511,13 @@
         <v>54</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K82" s="7">
         <v>660</v>
       </c>
       <c r="L82" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M82" s="3">
         <v>98</v>
@@ -11530,10 +11526,10 @@
         <v>98</v>
       </c>
       <c r="O82" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q82" s="3">
         <v>987725350</v>
@@ -11595,19 +11591,19 @@
     </row>
     <row r="83" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A83" s="18" t="s">
+        <v>427</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="D83" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="C83" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>432</v>
-      </c>
       <c r="E83" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F83" s="4">
         <v>2</v>
@@ -11622,7 +11618,7 @@
         <v>41</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="K83" s="7">
         <v>2703</v>
@@ -11637,10 +11633,10 @@
         <v>98</v>
       </c>
       <c r="O83" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q83" s="3">
         <v>992516280</v>
@@ -11702,19 +11698,19 @@
     </row>
     <row r="84" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A84" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>433</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>435</v>
       </c>
       <c r="F84" s="4">
         <v>2</v>
@@ -11729,7 +11725,7 @@
         <v>62</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K84" s="7">
         <v>2698</v>
@@ -11744,10 +11740,10 @@
         <v>98</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P84" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q84" s="3">
         <v>9611484889</v>
@@ -11809,19 +11805,19 @@
     </row>
     <row r="85" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A85" s="18" t="s">
+        <v>434</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="D85" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="E85" s="3" t="s">
         <v>438</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>440</v>
       </c>
       <c r="F85" s="4">
         <v>2</v>
@@ -11836,7 +11832,7 @@
         <v>45</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="K85" s="7">
         <v>1885</v>
@@ -11851,10 +11847,10 @@
         <v>98</v>
       </c>
       <c r="O85" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q85" s="3">
         <v>965408375</v>
@@ -11916,19 +11912,19 @@
     </row>
     <row r="86" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A86" s="20" t="s">
+        <v>731</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>732</v>
+      </c>
+      <c r="C86" s="12" t="s">
         <v>733</v>
       </c>
-      <c r="B86" s="12" t="s">
-        <v>734</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>735</v>
-      </c>
       <c r="D86" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F86" s="4">
         <v>1</v>
@@ -11943,13 +11939,13 @@
         <v>49</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="K86" s="7">
         <v>1443</v>
       </c>
       <c r="L86" s="10" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="M86" s="3">
         <v>98</v>
@@ -11958,10 +11954,10 @@
         <v>98</v>
       </c>
       <c r="O86" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P86" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q86" s="3">
         <v>988287059</v>
@@ -11970,7 +11966,7 @@
         <v>226291727</v>
       </c>
       <c r="S86" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="T86" s="3">
         <v>18</v>
@@ -12023,19 +12019,19 @@
     </row>
     <row r="87" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A87" s="20" t="s">
+        <v>735</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>736</v>
+      </c>
+      <c r="C87" s="12" t="s">
         <v>737</v>
       </c>
-      <c r="B87" s="12" t="s">
+      <c r="D87" s="12" t="s">
         <v>738</v>
       </c>
-      <c r="C87" s="12" t="s">
+      <c r="E87" s="12" t="s">
         <v>739</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>740</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>741</v>
       </c>
       <c r="F87" s="4">
         <v>1</v>
@@ -12050,7 +12046,7 @@
         <v>59</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="K87" s="7">
         <v>1228</v>
@@ -12065,10 +12061,10 @@
         <v>98</v>
       </c>
       <c r="O87" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P87" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q87" s="3">
         <v>993505415</v>
@@ -12130,19 +12126,19 @@
     </row>
     <row r="88" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A88" s="20" t="s">
+        <v>741</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>742</v>
+      </c>
+      <c r="C88" s="12" t="s">
         <v>743</v>
       </c>
-      <c r="B88" s="12" t="s">
+      <c r="D88" s="12" t="s">
         <v>744</v>
       </c>
-      <c r="C88" s="12" t="s">
+      <c r="E88" s="12" t="s">
         <v>745</v>
-      </c>
-      <c r="D88" s="12" t="s">
-        <v>746</v>
-      </c>
-      <c r="E88" s="12" t="s">
-        <v>747</v>
       </c>
       <c r="F88" s="4">
         <v>2</v>
@@ -12157,7 +12153,7 @@
         <v>56</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="K88" s="7">
         <v>2197</v>
@@ -12166,16 +12162,16 @@
         <v>98</v>
       </c>
       <c r="M88" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N88" s="5" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="O88" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P88" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q88" s="3">
         <v>972610137</v>
@@ -12237,19 +12233,19 @@
     </row>
     <row r="89" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A89" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="D89" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>445</v>
-      </c>
       <c r="E89" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F89" s="4">
         <v>2</v>
@@ -12264,7 +12260,7 @@
         <v>57</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="K89" s="7">
         <v>1819</v>
@@ -12279,10 +12275,10 @@
         <v>98</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q89" s="3">
         <v>958573062</v>
@@ -12344,19 +12340,19 @@
     </row>
     <row r="90" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A90" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="D90" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="E90" s="3" t="s">
         <v>449</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="F90" s="4">
         <v>1</v>
@@ -12371,13 +12367,13 @@
         <v>65</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K90" s="7">
         <v>1048</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M90" s="3">
         <v>98</v>
@@ -12386,10 +12382,10 @@
         <v>98</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P90" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q90" s="3">
         <v>969986839</v>
@@ -12451,19 +12447,19 @@
     </row>
     <row r="91" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A91" s="18" t="s">
+        <v>452</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="D91" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="C91" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>457</v>
-      </c>
       <c r="E91" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F91" s="4">
         <v>2</v>
@@ -12478,7 +12474,7 @@
         <v>70</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K91" s="7">
         <v>1738</v>
@@ -12493,10 +12489,10 @@
         <v>98</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P91" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q91" s="3">
         <v>963749574</v>
@@ -12558,19 +12554,19 @@
     </row>
     <row r="92" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A92" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="D92" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="E92" s="3" t="s">
         <v>461</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>463</v>
       </c>
       <c r="F92" s="4">
         <v>2</v>
@@ -12585,7 +12581,7 @@
         <v>46</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K92" s="7">
         <v>1004</v>
@@ -12600,10 +12596,10 @@
         <v>98</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P92" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q92" s="3">
         <v>961109149</v>
@@ -12665,19 +12661,19 @@
     </row>
     <row r="93" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A93" s="18" t="s">
+        <v>463</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="D93" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="E93" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>469</v>
       </c>
       <c r="F93" s="4">
         <v>1</v>
@@ -12692,7 +12688,7 @@
         <v>79</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K93" s="7">
         <v>427</v>
@@ -12707,10 +12703,10 @@
         <v>98</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P93" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q93" s="3">
         <v>976167293</v>
@@ -12772,19 +12768,19 @@
     </row>
     <row r="94" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A94" s="18" t="s">
+        <v>469</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="D94" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>474</v>
       </c>
       <c r="F94" s="4">
         <v>2</v>
@@ -12799,7 +12795,7 @@
         <v>44</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K94" s="7">
         <v>1890</v>
@@ -12814,10 +12810,10 @@
         <v>98</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P94" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q94" s="3">
         <v>973615437</v>
@@ -12879,19 +12875,19 @@
     </row>
     <row r="95" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A95" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="D95" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>477</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>479</v>
       </c>
       <c r="F95" s="4">
         <v>2</v>
@@ -12906,7 +12902,7 @@
         <v>65</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="K95" s="7">
         <v>781</v>
@@ -12921,10 +12917,10 @@
         <v>98</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q95" s="3">
         <v>985551984</v>
@@ -12986,19 +12982,19 @@
     </row>
     <row r="96" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A96" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="D96" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="E96" s="3" t="s">
         <v>483</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>485</v>
       </c>
       <c r="F96" s="4">
         <v>2</v>
@@ -13013,7 +13009,7 @@
         <v>59</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="K96" s="7">
         <v>3035</v>
@@ -13028,10 +13024,10 @@
         <v>98</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q96" s="3">
         <v>979765983</v>
@@ -13093,19 +13089,19 @@
     </row>
     <row r="97" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A97" s="18" t="s">
+        <v>486</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="D97" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="E97" s="3" t="s">
         <v>490</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>492</v>
       </c>
       <c r="F97" s="4">
         <v>1</v>
@@ -13120,7 +13116,7 @@
         <v>62</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="K97" s="7">
         <v>1963</v>
@@ -13135,10 +13131,10 @@
         <v>98</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q97" s="3">
         <v>965901004</v>
@@ -13200,19 +13196,19 @@
     </row>
     <row r="98" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A98" s="18" t="s">
+        <v>492</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="D98" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="E98" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>498</v>
       </c>
       <c r="F98" s="4">
         <v>2</v>
@@ -13227,7 +13223,7 @@
         <v>63</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="K98" s="7">
         <v>1951</v>
@@ -13242,10 +13238,10 @@
         <v>98</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q98" s="3">
         <v>977432422</v>
@@ -13307,19 +13303,19 @@
     </row>
     <row r="99" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A99" s="18" t="s">
+        <v>497</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="D99" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="C99" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>502</v>
-      </c>
       <c r="E99" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F99" s="4">
         <v>1</v>
@@ -13334,25 +13330,25 @@
         <v>70</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="K99" s="7">
         <v>420</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N99" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q99" s="3">
         <v>987743586</v>
@@ -13414,19 +13410,19 @@
     </row>
     <row r="100" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A100" s="18" t="s">
+        <v>504</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="D100" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="C100" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>509</v>
-      </c>
       <c r="E100" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F100" s="4">
         <v>2</v>
@@ -13441,7 +13437,7 @@
         <v>77</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K100" s="7">
         <v>2970</v>
@@ -13456,10 +13452,10 @@
         <v>98</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P100" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q100" s="3">
         <v>941839830</v>
@@ -13521,19 +13517,19 @@
     </row>
     <row r="101" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A101" s="18" t="s">
+        <v>509</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="D101" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>512</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>514</v>
       </c>
       <c r="F101" s="4">
         <v>2</v>
@@ -13548,7 +13544,7 @@
         <v>76</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="K101" s="7">
         <v>1416</v>
@@ -13563,10 +13559,10 @@
         <v>98</v>
       </c>
       <c r="O101" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P101" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q101" s="3">
         <v>993092514</v>
@@ -13628,19 +13624,19 @@
     </row>
     <row r="102" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A102" s="20" t="s">
+        <v>688</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>689</v>
+      </c>
+      <c r="C102" s="12" t="s">
         <v>690</v>
       </c>
-      <c r="B102" s="12" t="s">
-        <v>691</v>
-      </c>
-      <c r="C102" s="12" t="s">
-        <v>692</v>
-      </c>
       <c r="D102" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F102" s="4">
         <v>2</v>
@@ -13655,7 +13651,7 @@
         <v>65</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="K102" s="7">
         <v>2165</v>
@@ -13670,10 +13666,10 @@
         <v>98</v>
       </c>
       <c r="O102" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P102" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q102" s="3">
         <v>959885086</v>
@@ -13735,19 +13731,19 @@
     </row>
     <row r="103" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A103" s="18" t="s">
+        <v>514</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="D103" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E103" s="3" t="s">
         <v>517</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>519</v>
       </c>
       <c r="F103" s="4">
         <v>2</v>
@@ -13762,7 +13758,7 @@
         <v>48</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="K103" s="7">
         <v>1424</v>
@@ -13777,10 +13773,10 @@
         <v>98</v>
       </c>
       <c r="O103" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P103" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q103" s="3">
         <v>963546891</v>
@@ -13842,19 +13838,19 @@
     </row>
     <row r="104" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A104" s="18" t="s">
+        <v>519</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="D104" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="E104" s="3" t="s">
         <v>523</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>525</v>
       </c>
       <c r="F104" s="4">
         <v>2</v>
@@ -13869,13 +13865,13 @@
         <v>69</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K104" s="7">
         <v>1854</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="M104" s="3">
         <v>98</v>
@@ -13884,10 +13880,10 @@
         <v>98</v>
       </c>
       <c r="O104" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P104" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q104" s="3">
         <v>997974133</v>
@@ -13949,19 +13945,19 @@
     </row>
     <row r="105" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A105" s="20" t="s">
+        <v>752</v>
+      </c>
+      <c r="B105" s="12" t="s">
+        <v>753</v>
+      </c>
+      <c r="C105" s="12" t="s">
         <v>754</v>
       </c>
-      <c r="B105" s="12" t="s">
+      <c r="D105" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="E105" s="12" t="s">
         <v>755</v>
-      </c>
-      <c r="C105" s="12" t="s">
-        <v>756</v>
-      </c>
-      <c r="D105" s="12" t="s">
-        <v>427</v>
-      </c>
-      <c r="E105" s="12" t="s">
-        <v>757</v>
       </c>
       <c r="F105" s="4">
         <v>2</v>
@@ -13976,7 +13972,7 @@
         <v>67</v>
       </c>
       <c r="J105" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="K105" s="7">
         <v>2533</v>
@@ -13991,10 +13987,10 @@
         <v>98</v>
       </c>
       <c r="O105" s="12" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="P105" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q105" s="3">
         <v>920095328</v>
@@ -14056,19 +14052,19 @@
     </row>
     <row r="106" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A106" s="18" t="s">
+        <v>526</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>530</v>
-      </c>
       <c r="D106" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F106" s="4">
         <v>2</v>
@@ -14083,7 +14079,7 @@
         <v>55</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="K106" s="7">
         <v>1885</v>
@@ -14098,10 +14094,10 @@
         <v>98</v>
       </c>
       <c r="O106" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P106" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q106" s="3">
         <v>920377719</v>
@@ -14163,19 +14159,19 @@
     </row>
     <row r="107" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A107" s="18" t="s">
+        <v>530</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="D107" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="E107" s="3" t="s">
         <v>534</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>536</v>
       </c>
       <c r="F107" s="4">
         <v>2</v>
@@ -14190,7 +14186,7 @@
         <v>77</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="K107" s="7">
         <v>1584</v>
@@ -14205,10 +14201,10 @@
         <v>98</v>
       </c>
       <c r="O107" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P107" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q107" s="3">
         <v>994759636</v>
@@ -14270,16 +14266,16 @@
     </row>
     <row r="108" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A108" s="20" t="s">
+        <v>748</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>749</v>
+      </c>
+      <c r="C108" s="12" t="s">
         <v>750</v>
       </c>
-      <c r="B108" s="12" t="s">
+      <c r="D108" s="12" t="s">
         <v>751</v>
-      </c>
-      <c r="C108" s="12" t="s">
-        <v>752</v>
-      </c>
-      <c r="D108" s="12" t="s">
-        <v>753</v>
       </c>
       <c r="E108" s="3">
         <v>98</v>
@@ -14297,7 +14293,7 @@
         <v>51</v>
       </c>
       <c r="J108" s="12" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="K108" s="7">
         <v>1845</v>
@@ -14312,10 +14308,10 @@
         <v>98</v>
       </c>
       <c r="O108" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P108" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q108" s="3">
         <v>932801440</v>
@@ -14377,19 +14373,19 @@
     </row>
     <row r="109" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A109" s="18" t="s">
+        <v>536</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="D109" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="E109" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>541</v>
       </c>
       <c r="F109" s="4">
         <v>2</v>
@@ -14404,7 +14400,7 @@
         <v>76</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="K109" s="7">
         <v>1148</v>
@@ -14419,10 +14415,10 @@
         <v>98</v>
       </c>
       <c r="O109" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P109" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q109" s="3">
         <v>227323393</v>
@@ -14484,16 +14480,16 @@
     </row>
     <row r="110" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A110" s="18" t="s">
+        <v>541</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="D110" s="3" t="s">
         <v>544</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>546</v>
       </c>
       <c r="E110" s="3">
         <v>98</v>
@@ -14511,7 +14507,7 @@
         <v>71</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="K110" s="7">
         <v>2776</v>
@@ -14526,10 +14522,10 @@
         <v>98</v>
       </c>
       <c r="O110" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P110" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q110" s="3">
         <v>950095247</v>
@@ -14591,19 +14587,19 @@
     </row>
     <row r="111" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A111" s="18" t="s">
+        <v>546</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="D111" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="E111" s="3" t="s">
         <v>550</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>552</v>
       </c>
       <c r="F111" s="4">
         <v>2</v>
@@ -14618,7 +14614,7 @@
         <v>56</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="K111" s="7">
         <v>1605</v>
@@ -14633,10 +14629,10 @@
         <v>98</v>
       </c>
       <c r="O111" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="P111" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q111" s="3">
         <v>979960221</v>
@@ -14698,19 +14694,19 @@
     </row>
     <row r="112" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A112" s="18" t="s">
+        <v>553</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="D112" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="E112" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>559</v>
       </c>
       <c r="F112" s="4">
         <v>2</v>
@@ -14725,7 +14721,7 @@
         <v>62</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="K112" s="7">
         <v>2725</v>
@@ -14740,10 +14736,10 @@
         <v>98</v>
       </c>
       <c r="O112" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P112" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q112" s="3">
         <v>992074576</v>
@@ -14805,19 +14801,19 @@
     </row>
     <row r="113" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A113" s="18" t="s">
+        <v>559</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="D113" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="C113" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>564</v>
-      </c>
       <c r="E113" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F113" s="4">
         <v>1</v>
@@ -14832,7 +14828,7 @@
         <v>76</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="K113" s="7">
         <v>1870</v>
@@ -14847,10 +14843,10 @@
         <v>98</v>
       </c>
       <c r="O113" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P113" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q113" s="3">
         <v>99</v>
@@ -14912,19 +14908,19 @@
     </row>
     <row r="114" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A114" s="18" t="s">
+        <v>564</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="D114" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="C114" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>569</v>
-      </c>
       <c r="E114" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F114" s="4">
         <v>2</v>
@@ -14939,7 +14935,7 @@
         <v>62</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="K114" s="7">
         <v>1210</v>
@@ -14948,16 +14944,16 @@
         <v>98</v>
       </c>
       <c r="M114" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="N114" s="3">
         <v>98</v>
       </c>
       <c r="O114" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P114" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q114" s="3">
         <v>991710081</v>
@@ -15019,19 +15015,19 @@
     </row>
     <row r="115" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A115" s="18" t="s">
+        <v>569</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="D115" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="E115" s="3" t="s">
         <v>573</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>575</v>
       </c>
       <c r="F115" s="4">
         <v>2</v>
@@ -15046,7 +15042,7 @@
         <v>73</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="K115" s="7">
         <v>1421</v>
@@ -15061,10 +15057,10 @@
         <v>98</v>
       </c>
       <c r="O115" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P115" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q115" s="3">
         <v>976413412</v>
@@ -15126,19 +15122,19 @@
     </row>
     <row r="116" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A116" s="18" t="s">
+        <v>574</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="D116" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="E116" s="3" t="s">
         <v>578</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>580</v>
       </c>
       <c r="F116" s="4">
         <v>2</v>
@@ -15153,13 +15149,13 @@
         <v>38</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="K116" s="7">
         <v>1755</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="M116" s="3">
         <v>98</v>
@@ -15168,10 +15164,10 @@
         <v>98</v>
       </c>
       <c r="O116" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P116" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q116" s="3">
         <v>958774551</v>
@@ -15233,19 +15229,19 @@
     </row>
     <row r="117" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A117" s="18" t="s">
+        <v>581</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="D117" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="C117" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>586</v>
-      </c>
       <c r="E117" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F117" s="4">
         <v>1</v>
@@ -15260,7 +15256,7 @@
         <v>63</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="K117" s="7">
         <v>895</v>
@@ -15275,10 +15271,10 @@
         <v>98</v>
       </c>
       <c r="O117" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P117" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q117" s="3">
         <v>973895816</v>
@@ -15340,19 +15336,19 @@
     </row>
     <row r="118" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A118" s="18" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B118" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="D118" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C118" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="E118" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F118" s="4">
         <v>2</v>
@@ -15367,7 +15363,7 @@
         <v>52</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="K118" s="7">
         <v>1220</v>
@@ -15382,10 +15378,10 @@
         <v>98</v>
       </c>
       <c r="O118" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P118" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q118" s="3">
         <v>963392811</v>
@@ -15447,19 +15443,19 @@
     </row>
     <row r="119" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A119" s="18" t="s">
+        <v>589</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="B119" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>593</v>
-      </c>
       <c r="D119" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F119" s="4">
         <v>2</v>
@@ -15474,7 +15470,7 @@
         <v>59</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="K119" s="7">
         <v>992</v>
@@ -15489,10 +15485,10 @@
         <v>98</v>
       </c>
       <c r="O119" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P119" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q119" s="3">
         <v>973374326</v>
@@ -15554,19 +15550,19 @@
     </row>
     <row r="120" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A120" s="18" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F120" s="4">
         <v>2</v>
@@ -15581,7 +15577,7 @@
         <v>45</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="K120" s="7">
         <v>2774</v>
@@ -15590,16 +15586,16 @@
         <v>98</v>
       </c>
       <c r="M120" s="3" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="N120" s="3">
         <v>98</v>
       </c>
       <c r="O120" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P120" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q120" s="3">
         <v>950122513</v>
@@ -15661,50 +15657,50 @@
     </row>
     <row r="121" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A121" s="18" t="s">
+        <v>596</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="D121" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="E121" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="D121" s="3" t="s">
+      <c r="F121" s="4">
+        <v>1</v>
+      </c>
+      <c r="G121" s="12">
+        <v>99</v>
+      </c>
+      <c r="H121" s="7" t="s">
         <v>601</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="F121" s="4">
-        <v>1</v>
-      </c>
-      <c r="G121" s="12">
-        <v>99</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>603</v>
       </c>
       <c r="I121" s="3">
         <v>64</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="K121" s="7">
         <v>418</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="M121" s="3"/>
       <c r="N121" s="3">
         <v>98</v>
       </c>
       <c r="O121" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P121" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q121" s="3">
         <v>984642853</v>
@@ -15766,19 +15762,19 @@
     </row>
     <row r="122" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A122" s="18" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B122" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D122" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C122" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="E122" s="3" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F122" s="4">
         <v>2</v>
@@ -15793,7 +15789,7 @@
         <v>49</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K122" s="7">
         <v>2780</v>
@@ -15808,10 +15804,10 @@
         <v>98</v>
       </c>
       <c r="O122" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P122" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q122" s="3">
         <v>987385062</v>
@@ -15873,19 +15869,19 @@
     </row>
     <row r="123" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A123" s="18" t="s">
+        <v>605</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="D123" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="E123" s="3" t="s">
         <v>609</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>611</v>
       </c>
       <c r="F123" s="4">
         <v>1</v>
@@ -15900,7 +15896,7 @@
         <v>65</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="K123" s="7">
         <v>1369</v>
@@ -15915,10 +15911,10 @@
         <v>98</v>
       </c>
       <c r="O123" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P123" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q123" s="3">
         <v>986370378</v>
@@ -15980,19 +15976,19 @@
     </row>
     <row r="124" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A124" s="18" t="s">
+        <v>610</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="D124" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="C124" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>615</v>
-      </c>
       <c r="E124" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F124" s="4">
         <v>2</v>
@@ -16007,13 +16003,13 @@
         <v>58</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="K124" s="7">
         <v>1460</v>
       </c>
       <c r="L124" s="4" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="M124" s="3">
         <v>98</v>
@@ -16022,10 +16018,10 @@
         <v>98</v>
       </c>
       <c r="O124" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P124" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q124" s="3">
         <v>984670171</v>
@@ -16087,19 +16083,19 @@
     </row>
     <row r="125" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A125" s="20" t="s">
+        <v>698</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>699</v>
+      </c>
+      <c r="C125" s="12" t="s">
         <v>700</v>
       </c>
-      <c r="B125" s="12" t="s">
+      <c r="D125" s="12" t="s">
         <v>701</v>
       </c>
-      <c r="C125" s="12" t="s">
-        <v>702</v>
-      </c>
-      <c r="D125" s="12" t="s">
-        <v>703</v>
-      </c>
       <c r="E125" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F125" s="4">
         <v>1</v>
@@ -16114,7 +16110,7 @@
         <v>88</v>
       </c>
       <c r="J125" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K125" s="7">
         <v>1198</v>
@@ -16129,10 +16125,10 @@
         <v>98</v>
       </c>
       <c r="O125" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P125" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q125" s="3">
         <v>991787604</v>
@@ -16194,34 +16190,34 @@
     </row>
     <row r="126" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A126" s="20" t="s">
+        <v>692</v>
+      </c>
+      <c r="B126" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="C126" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="B126" s="12" t="s">
+      <c r="D126" s="12" t="s">
         <v>695</v>
       </c>
-      <c r="C126" s="12" t="s">
+      <c r="E126" s="12" t="s">
         <v>696</v>
       </c>
-      <c r="D126" s="12" t="s">
+      <c r="F126" s="4">
+        <v>1</v>
+      </c>
+      <c r="G126" s="12">
+        <v>99</v>
+      </c>
+      <c r="H126" s="21" t="s">
         <v>697</v>
-      </c>
-      <c r="E126" s="12" t="s">
-        <v>698</v>
-      </c>
-      <c r="F126" s="4">
-        <v>1</v>
-      </c>
-      <c r="G126" s="12">
-        <v>99</v>
-      </c>
-      <c r="H126" s="21" t="s">
-        <v>699</v>
       </c>
       <c r="I126" s="3">
         <v>82</v>
       </c>
       <c r="J126" s="12" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="K126" s="7">
         <v>888</v>
@@ -16236,10 +16232,10 @@
         <v>98</v>
       </c>
       <c r="O126" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P126" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q126" s="3">
         <v>996351694</v>
@@ -16301,19 +16297,19 @@
     </row>
     <row r="127" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A127" s="20" t="s">
+        <v>702</v>
+      </c>
+      <c r="B127" s="12" t="s">
+        <v>703</v>
+      </c>
+      <c r="C127" s="12" t="s">
         <v>704</v>
       </c>
-      <c r="B127" s="12" t="s">
+      <c r="D127" s="12" t="s">
         <v>705</v>
       </c>
-      <c r="C127" s="12" t="s">
-        <v>706</v>
-      </c>
-      <c r="D127" s="12" t="s">
-        <v>707</v>
-      </c>
       <c r="E127" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F127" s="4">
         <v>2</v>
@@ -16328,7 +16324,7 @@
         <v>52</v>
       </c>
       <c r="J127" s="12" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="K127" s="7">
         <v>1741</v>
@@ -16343,10 +16339,10 @@
         <v>98</v>
       </c>
       <c r="O127" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P127" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q127" s="3">
         <v>933843269</v>
@@ -16408,19 +16404,19 @@
     </row>
     <row r="128" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A128" s="18" t="s">
+        <v>616</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="D128" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B128" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="C128" s="3" t="s">
+      <c r="E128" s="3" t="s">
         <v>619</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>621</v>
       </c>
       <c r="F128" s="4">
         <v>2</v>
@@ -16435,7 +16431,7 @@
         <v>61</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="K128" s="7">
         <v>1487</v>
@@ -16450,10 +16446,10 @@
         <v>98</v>
       </c>
       <c r="O128" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P128" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q128" s="3">
         <v>956161036</v>
@@ -16515,19 +16511,19 @@
     </row>
     <row r="129" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A129" s="18" t="s">
+        <v>621</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>758</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="D129" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="B129" s="12" t="s">
-        <v>760</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>625</v>
-      </c>
       <c r="E129" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F129" s="4">
         <v>2</v>
@@ -16542,25 +16538,25 @@
         <v>69</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="K129" s="7">
         <v>1017</v>
       </c>
       <c r="L129" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M129" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N129" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="O129" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P129" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q129" s="3">
         <v>945257681</v>
@@ -16622,19 +16618,19 @@
     </row>
     <row r="130" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A130" s="20" t="s">
+        <v>757</v>
+      </c>
+      <c r="B130" s="12" t="s">
         <v>759</v>
       </c>
-      <c r="B130" s="12" t="s">
+      <c r="C130" s="12" t="s">
+        <v>760</v>
+      </c>
+      <c r="D130" s="12" t="s">
         <v>761</v>
       </c>
-      <c r="C130" s="12" t="s">
-        <v>762</v>
-      </c>
-      <c r="D130" s="12" t="s">
-        <v>763</v>
-      </c>
       <c r="E130" s="12" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F130" s="4">
         <v>2</v>
@@ -16649,7 +16645,7 @@
         <v>61</v>
       </c>
       <c r="J130" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="K130" s="7">
         <v>2539</v>
@@ -16661,13 +16657,13 @@
         <v>98</v>
       </c>
       <c r="N130" s="10" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="O130" s="12" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="P130" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q130" s="3">
         <v>94198781</v>
@@ -16729,19 +16725,19 @@
     </row>
     <row r="131" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A131" s="18" t="s">
+        <v>626</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C131" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="D131" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="E131" s="3" t="s">
         <v>630</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="E131" s="3" t="s">
-        <v>632</v>
       </c>
       <c r="F131" s="4">
         <v>2</v>
@@ -16756,7 +16752,7 @@
         <v>54</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="K131" s="7">
         <v>409</v>
@@ -16771,10 +16767,10 @@
         <v>98</v>
       </c>
       <c r="O131" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P131" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q131" s="3">
         <v>994756112</v>
@@ -16836,19 +16832,19 @@
     </row>
     <row r="132" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A132" s="18" t="s">
+        <v>632</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="C132" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="D132" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E132" s="3" t="s">
         <v>635</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>637</v>
       </c>
       <c r="F132" s="4">
         <v>2</v>
@@ -16863,7 +16859,7 @@
         <v>60</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="K132" s="7">
         <v>2780</v>
@@ -16875,13 +16871,13 @@
         <v>98</v>
       </c>
       <c r="N132" s="4" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="O132" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P132" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q132" s="3">
         <v>937364998</v>

--- a/Input/instrumento n6_cp2_limpio.xlsx
+++ b/Input/instrumento n6_cp2_limpio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0340f46c4e5df8d5/Escritorio/Cuidados/Input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0340f46c4e5df8d5/Escritorio/OPT_R1/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="989" documentId="13_ncr:1_{E42A7D12-2DF1-41EF-9304-A16BC4052AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B74F791-0128-401E-9D10-00E6E4074360}"/>
+  <xr:revisionPtr revIDLastSave="991" documentId="13_ncr:1_{E42A7D12-2DF1-41EF-9304-A16BC4052AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F62A811-FE9C-435D-AE4D-31D21902C8C2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F491E6BB-27A6-4656-8C8B-02D8962D134E}"/>
   </bookViews>
@@ -1934,9 +1934,6 @@
     <t>Coronel López de Alcazar</t>
   </si>
   <si>
-    <t>Zunilda Escudero</t>
-  </si>
-  <si>
     <t>8.006.766-6</t>
   </si>
   <si>
@@ -2352,6 +2349,9 @@
   </si>
   <si>
     <t>Teléfono_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zunilda Escobedo Concha </t>
   </si>
 </sst>
 </file>
@@ -2492,6 +2492,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2819,7 +2823,7 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2834,7 +2838,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -2867,34 +2871,34 @@
         <v>13</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>644</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>645</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>15</v>
@@ -3996,19 +4000,19 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
+        <v>645</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>649</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>650</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -4023,7 +4027,7 @@
         <v>22</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="K12" s="7">
         <v>1666</v>
@@ -4424,16 +4428,16 @@
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
+        <v>651</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>654</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>655</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>222</v>
@@ -4442,7 +4446,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H16" s="8">
         <v>34954</v>
@@ -4530,7 +4534,7 @@
       </c>
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="20" t="s">
         <v>106</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -4959,25 +4963,25 @@
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
+        <v>762</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>763</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="C21" s="12" t="s">
         <v>764</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>765</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>169</v>
       </c>
       <c r="E21" s="12" t="s">
+        <v>765</v>
+      </c>
+      <c r="F21" s="4">
+        <v>2</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>766</v>
-      </c>
-      <c r="F21" s="4">
-        <v>2</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>767</v>
       </c>
       <c r="H21" s="8">
         <v>16737</v>
@@ -4986,7 +4990,7 @@
         <v>80</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="K21" s="3">
         <v>1235</v>
@@ -4998,7 +5002,7 @@
         <v>223</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="O21" s="12" t="s">
         <v>30</v>
@@ -5922,16 +5926,16 @@
     </row>
     <row r="30" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A30" s="20" t="s">
+        <v>706</v>
+      </c>
+      <c r="B30" s="12" t="s">
         <v>707</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="C30" s="12" t="s">
         <v>708</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="D30" s="12" t="s">
         <v>709</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>710</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>182</v>
@@ -5949,7 +5953,7 @@
         <v>63</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="K30" s="3">
         <v>1198</v>
@@ -6350,19 +6354,19 @@
     </row>
     <row r="34" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A34" s="18" t="s">
+        <v>656</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>659</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>660</v>
       </c>
       <c r="F34" s="4">
         <v>2</v>
@@ -6389,7 +6393,7 @@
         <v>595</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="O34" s="3" t="s">
         <v>30</v>
@@ -6778,19 +6782,19 @@
     </row>
     <row r="38" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A38" s="18" t="s">
+        <v>662</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>665</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>666</v>
       </c>
       <c r="F38" s="4">
         <v>2</v>
@@ -6805,7 +6809,7 @@
         <v>59</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K38" s="3">
         <v>987</v>
@@ -7206,19 +7210,19 @@
     </row>
     <row r="42" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A42" s="20" t="s">
+        <v>711</v>
+      </c>
+      <c r="B42" s="12" t="s">
         <v>712</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="C42" s="12" t="s">
         <v>713</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="D42" s="12" t="s">
         <v>714</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>715</v>
-      </c>
       <c r="E42" s="12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F42" s="4">
         <v>1</v>
@@ -7233,7 +7237,7 @@
         <v>78</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="K42" s="3">
         <v>1468</v>
@@ -7245,7 +7249,7 @@
         <v>98</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="O42" s="12" t="s">
         <v>30</v>
@@ -7313,25 +7317,25 @@
     </row>
     <row r="43" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A43" s="20" t="s">
+        <v>717</v>
+      </c>
+      <c r="B43" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="C43" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="D43" s="12" t="s">
         <v>720</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="E43" s="12" t="s">
         <v>721</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="F43" s="4">
+        <v>2</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>722</v>
-      </c>
-      <c r="F43" s="4">
-        <v>2</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>723</v>
       </c>
       <c r="H43" s="8">
         <v>24437</v>
@@ -7340,13 +7344,13 @@
         <v>59</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="K43" s="3">
         <v>2716</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="M43" s="3">
         <v>98</v>
@@ -9132,7 +9136,7 @@
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A60" s="18" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>547</v>
@@ -9141,7 +9145,7 @@
         <v>548</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>550</v>
@@ -9451,13 +9455,13 @@
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A63" s="20" t="s">
+        <v>725</v>
+      </c>
+      <c r="B63" s="12" t="s">
         <v>726</v>
       </c>
-      <c r="B63" s="12" t="s">
+      <c r="C63" s="12" t="s">
         <v>727</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>728</v>
       </c>
       <c r="D63" s="12" t="s">
         <v>187</v>
@@ -9478,13 +9482,13 @@
         <v>84</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K63" s="3">
         <v>1499</v>
       </c>
       <c r="L63" s="10" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="M63" s="3">
         <v>98</v>
@@ -10307,16 +10311,16 @@
     </row>
     <row r="71" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A71" s="18" t="s">
+        <v>670</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>673</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>674</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>36</v>
@@ -10334,13 +10338,13 @@
         <v>72</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="K71" s="3">
         <v>1699</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="M71" s="3">
         <v>98</v>
@@ -10414,16 +10418,16 @@
     </row>
     <row r="72" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A72" s="20" t="s">
+        <v>676</v>
+      </c>
+      <c r="B72" s="12" t="s">
         <v>677</v>
       </c>
-      <c r="B72" s="12" t="s">
+      <c r="C72" s="12" t="s">
         <v>678</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="D72" s="12" t="s">
         <v>679</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>680</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>90</v>
@@ -10447,7 +10451,7 @@
         <v>1021</v>
       </c>
       <c r="L72" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="M72" s="12" t="s">
         <v>203</v>
@@ -10521,19 +10525,19 @@
     </row>
     <row r="73" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A73" s="20" t="s">
+        <v>681</v>
+      </c>
+      <c r="B73" s="12" t="s">
         <v>682</v>
       </c>
-      <c r="B73" s="12" t="s">
+      <c r="C73" s="12" t="s">
         <v>683</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="D73" s="12" t="s">
         <v>684</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="E73" s="12" t="s">
         <v>685</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>686</v>
       </c>
       <c r="F73" s="4">
         <v>2</v>
@@ -10563,7 +10567,7 @@
         <v>98</v>
       </c>
       <c r="O73" s="12" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="P73" s="12" t="s">
         <v>31</v>
@@ -11912,19 +11916,19 @@
     </row>
     <row r="86" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A86" s="20" t="s">
+        <v>730</v>
+      </c>
+      <c r="B86" s="12" t="s">
         <v>731</v>
       </c>
-      <c r="B86" s="12" t="s">
+      <c r="C86" s="12" t="s">
         <v>732</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>733</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>200</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F86" s="4">
         <v>1</v>
@@ -11945,7 +11949,7 @@
         <v>1443</v>
       </c>
       <c r="L86" s="10" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="M86" s="3">
         <v>98</v>
@@ -12019,19 +12023,19 @@
     </row>
     <row r="87" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A87" s="20" t="s">
+        <v>734</v>
+      </c>
+      <c r="B87" s="12" t="s">
         <v>735</v>
       </c>
-      <c r="B87" s="12" t="s">
+      <c r="C87" s="12" t="s">
         <v>736</v>
       </c>
-      <c r="C87" s="12" t="s">
+      <c r="D87" s="12" t="s">
         <v>737</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="E87" s="12" t="s">
         <v>738</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>739</v>
       </c>
       <c r="F87" s="4">
         <v>1</v>
@@ -12046,7 +12050,7 @@
         <v>59</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="K87" s="7">
         <v>1228</v>
@@ -12126,19 +12130,19 @@
     </row>
     <row r="88" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A88" s="20" t="s">
+        <v>740</v>
+      </c>
+      <c r="B88" s="12" t="s">
         <v>741</v>
       </c>
-      <c r="B88" s="12" t="s">
+      <c r="C88" s="12" t="s">
         <v>742</v>
       </c>
-      <c r="C88" s="12" t="s">
+      <c r="D88" s="12" t="s">
         <v>743</v>
       </c>
-      <c r="D88" s="12" t="s">
+      <c r="E88" s="12" t="s">
         <v>744</v>
-      </c>
-      <c r="E88" s="12" t="s">
-        <v>745</v>
       </c>
       <c r="F88" s="4">
         <v>2</v>
@@ -12153,7 +12157,7 @@
         <v>56</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="K88" s="7">
         <v>2197</v>
@@ -12165,7 +12169,7 @@
         <v>203</v>
       </c>
       <c r="N88" s="5" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="O88" s="12" t="s">
         <v>30</v>
@@ -13624,13 +13628,13 @@
     </row>
     <row r="102" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A102" s="20" t="s">
+        <v>687</v>
+      </c>
+      <c r="B102" s="12" t="s">
         <v>688</v>
       </c>
-      <c r="B102" s="12" t="s">
+      <c r="C102" s="12" t="s">
         <v>689</v>
-      </c>
-      <c r="C102" s="12" t="s">
-        <v>690</v>
       </c>
       <c r="D102" s="12" t="s">
         <v>53</v>
@@ -13651,7 +13655,7 @@
         <v>65</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="K102" s="7">
         <v>2165</v>
@@ -13945,19 +13949,19 @@
     </row>
     <row r="105" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A105" s="20" t="s">
+        <v>751</v>
+      </c>
+      <c r="B105" s="12" t="s">
         <v>752</v>
       </c>
-      <c r="B105" s="12" t="s">
+      <c r="C105" s="12" t="s">
         <v>753</v>
-      </c>
-      <c r="C105" s="12" t="s">
-        <v>754</v>
       </c>
       <c r="D105" s="12" t="s">
         <v>425</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F105" s="4">
         <v>2</v>
@@ -13987,7 +13991,7 @@
         <v>98</v>
       </c>
       <c r="O105" s="12" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="P105" s="12" t="s">
         <v>31</v>
@@ -14266,16 +14270,16 @@
     </row>
     <row r="108" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A108" s="20" t="s">
+        <v>747</v>
+      </c>
+      <c r="B108" s="12" t="s">
         <v>748</v>
       </c>
-      <c r="B108" s="12" t="s">
+      <c r="C108" s="12" t="s">
         <v>749</v>
       </c>
-      <c r="C108" s="12" t="s">
+      <c r="D108" s="12" t="s">
         <v>750</v>
-      </c>
-      <c r="D108" s="12" t="s">
-        <v>751</v>
       </c>
       <c r="E108" s="3">
         <v>98</v>
@@ -16083,16 +16087,16 @@
     </row>
     <row r="125" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A125" s="20" t="s">
+        <v>697</v>
+      </c>
+      <c r="B125" s="12" t="s">
         <v>698</v>
       </c>
-      <c r="B125" s="12" t="s">
+      <c r="C125" s="12" t="s">
         <v>699</v>
       </c>
-      <c r="C125" s="12" t="s">
+      <c r="D125" s="12" t="s">
         <v>700</v>
-      </c>
-      <c r="D125" s="12" t="s">
-        <v>701</v>
       </c>
       <c r="E125" s="12" t="s">
         <v>47</v>
@@ -16190,28 +16194,28 @@
     </row>
     <row r="126" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A126" s="20" t="s">
+        <v>691</v>
+      </c>
+      <c r="B126" s="12" t="s">
         <v>692</v>
       </c>
-      <c r="B126" s="12" t="s">
+      <c r="C126" s="12" t="s">
         <v>693</v>
       </c>
-      <c r="C126" s="12" t="s">
+      <c r="D126" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="D126" s="12" t="s">
+      <c r="E126" s="12" t="s">
         <v>695</v>
       </c>
-      <c r="E126" s="12" t="s">
+      <c r="F126" s="4">
+        <v>1</v>
+      </c>
+      <c r="G126" s="12">
+        <v>99</v>
+      </c>
+      <c r="H126" s="21" t="s">
         <v>696</v>
-      </c>
-      <c r="F126" s="4">
-        <v>1</v>
-      </c>
-      <c r="G126" s="12">
-        <v>99</v>
-      </c>
-      <c r="H126" s="21" t="s">
-        <v>697</v>
       </c>
       <c r="I126" s="3">
         <v>82</v>
@@ -16297,16 +16301,16 @@
     </row>
     <row r="127" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A127" s="20" t="s">
+        <v>701</v>
+      </c>
+      <c r="B127" s="12" t="s">
         <v>702</v>
       </c>
-      <c r="B127" s="12" t="s">
+      <c r="C127" s="12" t="s">
         <v>703</v>
       </c>
-      <c r="C127" s="12" t="s">
+      <c r="D127" s="12" t="s">
         <v>704</v>
-      </c>
-      <c r="D127" s="12" t="s">
-        <v>705</v>
       </c>
       <c r="E127" s="12" t="s">
         <v>121</v>
@@ -16324,7 +16328,7 @@
         <v>52</v>
       </c>
       <c r="J127" s="12" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="K127" s="7">
         <v>1741</v>
@@ -16514,7 +16518,7 @@
         <v>621</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>622</v>
@@ -16618,16 +16622,16 @@
     </row>
     <row r="130" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A130" s="20" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B130" s="12" t="s">
+        <v>758</v>
+      </c>
+      <c r="C130" s="12" t="s">
         <v>759</v>
       </c>
-      <c r="C130" s="12" t="s">
+      <c r="D130" s="12" t="s">
         <v>760</v>
-      </c>
-      <c r="D130" s="12" t="s">
-        <v>761</v>
       </c>
       <c r="E130" s="12" t="s">
         <v>402</v>
@@ -16657,10 +16661,10 @@
         <v>98</v>
       </c>
       <c r="N130" s="10" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="O130" s="12" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="P130" s="12" t="s">
         <v>31</v>
@@ -16832,19 +16836,19 @@
     </row>
     <row r="132" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A132" s="18" t="s">
+        <v>771</v>
+      </c>
+      <c r="B132" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="C132" s="3" t="s">
         <v>633</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>634</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F132" s="4">
         <v>2</v>
@@ -16871,7 +16875,7 @@
         <v>98</v>
       </c>
       <c r="N132" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="O132" s="3" t="s">
         <v>30</v>
